--- a/docs/tenders.xlsx
+++ b/docs/tenders.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Construction tenders" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Construction tenders'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Construction tenders'!$A$1:$I$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -528,94 +528,10 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Dezvoltarea SNT în vederea alimentării cu gaze naturale a localităților din centrul și Nord – Estul județului Botoșani, Lot 1, Lot 2, Lot 3, Lot 4</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RO13068733 - Societatea Nationala de Transport Gaze Naturale TRANSGAZ SA</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>167826498.17</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>45231220-3 - Lucrari de constructii de gazoducte (Rev.2)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Licitatie deschisa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CN1096645</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://www.e-licitatie.ro/pub/notices/c-notice/v2/view/100212283</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Conductă de transport gaze naturale Huedin-Lugașu (inclusiv alimentare cu energie electrică, protecție catodică și fibră optică) LOT 1, PT nr. TG_INV_10035/2021</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RO13068733 - Societatea Nationala de Transport Gaze Naturale TRANSGAZ SA</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>108866831.21</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>45231220-3 - Lucrari de constructii de gazoducte (Rev.2)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Licitatie deschisa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CN1096647</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>https://www.e-licitatie.ro/pub/notices/c-notice/v2/view/100212284</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:I2"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/tenders.xlsx
+++ b/docs/tenders.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Construction tenders" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Construction tenders'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Construction tenders'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,10 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -487,52 +486,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Modernizarea Stației de Măsurare Gaze Naturale SMG Negru Vodă – 2 loturi</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RO13068733 - Societatea Nationala de Transport Gaze Naturale TRANSGAZ SA</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>284057371.37</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>45255121-3 - Lucrari de constructii de instalatii de suprafata (Rev.2)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Licitatie deschisa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>CN1096727</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://www.e-licitatie.ro/pub/notices/c-notice/v2/view/100212366</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
-  </hyperlinks>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>